--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7565E5-F42B-4F54-B75B-42624D601925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743F988A-5D3F-4291-A995-88B5FBCFBAB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="3144" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" sheetId="1" r:id="rId1"/>
-    <sheet name="Projects" sheetId="2" r:id="rId2"/>
+    <sheet name="Login" sheetId="3" r:id="rId1"/>
+    <sheet name="Customer" sheetId="1" r:id="rId2"/>
+    <sheet name="Project" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Project_Name</t>
   </si>
@@ -69,9 +70,6 @@
     <t>Company</t>
   </si>
   <si>
-    <t>VAT_Number</t>
-  </si>
-  <si>
     <t>Phone</t>
   </si>
   <si>
@@ -112,13 +110,61 @@
   </si>
   <si>
     <t>VietNam</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>TCs</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>loginSuccess</t>
+  </si>
+  <si>
+    <t>admin@example.com</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>admin123@example.com</t>
+  </si>
+  <si>
+    <t>2222222</t>
+  </si>
+  <si>
+    <t>loginFailWithEmailInvalid</t>
+  </si>
+  <si>
+    <t>loginFailWithPassInvalid</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Công ty Ween</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,13 +172,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="1">
@@ -147,8 +208,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,77 +548,144 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1129EC2-D029-48F9-827C-BCE01AB8E176}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="16.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D93C7CD2-8E73-43DE-94E6-3A28F5CAF450}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2">
-        <v>7000</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1129EC2-D029-48F9-827C-BCE01AB8E176}">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultColWidth="16.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K3" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FC15DE-0E0A-485E-AD31-E7992A0D7BD7}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743F988A-5D3F-4291-A995-88B5FBCFBAB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44EC38FB-0E23-4BAA-93E5-765A185308E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3144" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>Project_Name</t>
   </si>
@@ -97,9 +97,6 @@
     <t>028yyzzxxx</t>
   </si>
   <si>
-    <t>vinhtuong.com.vn</t>
-  </si>
-  <si>
     <t>VIP</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>Q1</t>
   </si>
   <si>
-    <t>VietNam</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -154,16 +148,29 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Vietnamese</t>
+  </si>
+  <si>
+    <t>Vietnam</t>
+  </si>
+  <si>
+    <t>Công ty GM</t>
+  </si>
+  <si>
+    <t>gmyhl.com.vn</t>
+  </si>
+  <si>
     <t>Passed</t>
-  </si>
-  <si>
-    <t>Công ty Ween</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -179,7 +186,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -195,6 +202,9 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill/>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -208,11 +218,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -553,47 +566,47 @@
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>25</v>
-      </c>
-      <c r="B1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
         <v>31</v>
       </c>
+      <c r="B3" t="s" s="0">
+        <v>29</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -604,15 +617,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1129EC2-D029-48F9-827C-BCE01AB8E176}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="16.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>9</v>
@@ -624,59 +637,63 @@
         <v>11</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="K3" s="3" t="s">
+      <c r="K2" t="s" s="0">
         <v>37</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -691,28 +708,28 @@
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
     </row>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44EC38FB-0E23-4BAA-93E5-765A185308E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F663439C-956C-4498-8BA9-9AD00B2ACFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>Project_Name</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Customer</t>
   </si>
   <si>
-    <t>Total_Rate</t>
-  </si>
-  <si>
     <t>Estimated_Hours</t>
   </si>
   <si>
@@ -103,9 +100,6 @@
     <t>HCM</t>
   </si>
   <si>
-    <t>Q1</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -157,20 +151,67 @@
     <t>Vietnam</t>
   </si>
   <si>
-    <t>Công ty GM</t>
-  </si>
-  <si>
-    <t>gmyhl.com.vn</t>
-  </si>
-  <si>
     <t>Passed</t>
+  </si>
+  <si>
+    <t>Billing_Type</t>
+  </si>
+  <si>
+    <t>Mua hàng qua app</t>
+  </si>
+  <si>
+    <t>Task Hours</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Project Manager, Admin Anh Tester, Admin Example</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>14-04-2026</t>
+  </si>
+  <si>
+    <t>Members</t>
+  </si>
+  <si>
+    <t>14-05-2026</t>
+  </si>
+  <si>
+    <t>vtyhl.com.vn</t>
+  </si>
+  <si>
+    <t>Bình Thạnh</t>
+  </si>
+  <si>
+    <t>Giá cả hợp lý, chất liệu hợp thời</t>
+  </si>
+  <si>
+    <t>URL_Customer</t>
+  </si>
+  <si>
+    <t>Công ty VT YHL 19/04</t>
+  </si>
+  <si>
+    <t>https://crm.anhtester.com/admin/clients/client/9028</t>
+  </si>
+  <si>
+    <t>Điền thông tin</t>
+  </si>
+  <si>
+    <t>Check thông tin</t>
+  </si>
+  <si>
+    <t>Thạch cao, Khung</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -186,7 +227,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -202,9 +243,6 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
-    <fill>
-      <patternFill/>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -218,14 +256,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,47 +601,47 @@
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
         <v>23</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="0">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>27</v>
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -617,83 +652,89 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1129EC2-D029-48F9-827C-BCE01AB8E176}">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultColWidth="16.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s" s="0">
+      <c r="L2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>40</v>
+      <c r="M2" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -704,33 +745,87 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FC15DE-0E0A-485E-AD31-E7992A0D7BD7}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="G1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="0">
-        <v>7</v>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="str">
+        <f xml:space="preserve"> Customer!A2</f>
+        <v>Công ty VT YHL 19/04</v>
+      </c>
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="str">
+        <f>Customer!M2</f>
+        <v>https://crm.anhtester.com/admin/clients/client/9028</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F663439C-956C-4498-8BA9-9AD00B2ACFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E210F512-68FD-4545-A250-C5558BC62282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="3144" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t>Project_Name</t>
   </si>
@@ -193,9 +193,6 @@
     <t>URL_Customer</t>
   </si>
   <si>
-    <t>Công ty VT YHL 19/04</t>
-  </si>
-  <si>
     <t>https://crm.anhtester.com/admin/clients/client/9028</t>
   </si>
   <si>
@@ -206,12 +203,19 @@
   </si>
   <si>
     <t>Thạch cao, Khung</t>
+  </si>
+  <si>
+    <t>Công ty RM</t>
+  </si>
+  <si>
+    <t>https://crm.anhtester.com/admin/clients/client/9030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -227,7 +231,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -243,6 +247,9 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill/>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -256,11 +263,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -601,21 +614,21 @@
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -623,10 +636,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -634,10 +647,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -697,44 +710,44 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>50</v>
+      <c r="A2" t="s" s="0">
+        <v>54</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>47</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>51</v>
+      <c r="M2" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -748,82 +761,82 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" customWidth="true" width="18.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" t="str" s="0">
         <f xml:space="preserve"> Customer!A2</f>
-        <v>Công ty VT YHL 19/04</v>
-      </c>
-      <c r="D2" t="s">
+        <v>Công ty RM</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>40</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="J2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J2" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="K2" t="s" s="0">
         <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="str">
+      <c r="A3" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C3" t="str" s="0">
         <f>Customer!M2</f>
         <v>https://crm.anhtester.com/admin/clients/client/9028</v>
       </c>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E210F512-68FD-4545-A250-C5558BC62282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AAEA5B-85DF-498D-B12D-E4168A37C4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3144" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="1872" yWindow="912" windowWidth="19944" windowHeight="11328" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>Project_Name</t>
   </si>
@@ -145,15 +145,9 @@
     <t>Language</t>
   </si>
   <si>
-    <t>Vietnamese</t>
-  </si>
-  <si>
     <t>Vietnam</t>
   </si>
   <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>Billing_Type</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>URL_Customer</t>
   </si>
   <si>
-    <t>https://crm.anhtester.com/admin/clients/client/9028</t>
-  </si>
-  <si>
     <t>Điền thông tin</t>
   </si>
   <si>
@@ -205,17 +196,22 @@
     <t>Thạch cao, Khung</t>
   </si>
   <si>
-    <t>Công ty RM</t>
-  </si>
-  <si>
-    <t>https://crm.anhtester.com/admin/clients/client/9030</t>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Công ty Hải Lê</t>
+  </si>
+  <si>
+    <t>Japanese</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -231,7 +227,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,9 +243,6 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
-    <fill>
-      <patternFill/>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -263,17 +256,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -614,21 +601,21 @@
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -636,10 +623,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -647,10 +634,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -665,10 +652,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1129EC2-D029-48F9-827C-BCE01AB8E176}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -685,70 +672,72 @@
         <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>49</v>
+      <c r="N1" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>54</v>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -761,84 +750,84 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" customWidth="true" width="18.5546875"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="B1" t="s" s="0">
+      <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="E1" t="s" s="0">
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="H1" t="s" s="0">
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="str">
+        <f xml:space="preserve"> Customer!A2</f>
+        <v>Công ty Hải Lê</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="str" s="0">
-        <f xml:space="preserve"> Customer!A2</f>
-        <v>Công ty RM</v>
-      </c>
-      <c r="D2" t="s" s="0">
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" t="s" s="0">
+      <c r="H2" t="s">
         <v>41</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="I2" t="s">
         <v>43</v>
       </c>
-      <c r="I2" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="K2" t="s" s="0">
-        <v>48</v>
+      <c r="J2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="C3" t="str" s="0">
-        <f>Customer!M2</f>
-        <v>https://crm.anhtester.com/admin/clients/client/9028</v>
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3">
+        <f>Customer!N2</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AAEA5B-85DF-498D-B12D-E4168A37C4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D796507-C72F-4C1A-9057-ECD9C2EB8BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1872" yWindow="912" windowWidth="19944" windowHeight="11328" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="2136" yWindow="708" windowWidth="19944" windowHeight="11328" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="87">
   <si>
     <t>Project_Name</t>
   </si>
@@ -187,25 +187,121 @@
     <t>URL_Customer</t>
   </si>
   <si>
-    <t>Điền thông tin</t>
-  </si>
-  <si>
-    <t>Check thông tin</t>
-  </si>
-  <si>
-    <t>Thạch cao, Khung</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
     <t>USD</t>
   </si>
   <si>
-    <t>Công ty Hải Lê</t>
-  </si>
-  <si>
     <t>Japanese</t>
+  </si>
+  <si>
+    <t>Thạch cao</t>
+  </si>
+  <si>
+    <t>Project_Number</t>
+  </si>
+  <si>
+    <t>Mua hàng online</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>01-05-2026</t>
+  </si>
+  <si>
+    <t>30-05-2026</t>
+  </si>
+  <si>
+    <t>online</t>
+  </si>
+  <si>
+    <t>Ở đâu cũng mua được</t>
+  </si>
+  <si>
+    <t>2383</t>
+  </si>
+  <si>
+    <t>Testcase</t>
+  </si>
+  <si>
+    <t>ADD</t>
+  </si>
+  <si>
+    <t>EDIT</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>01-06-2026</t>
+  </si>
+  <si>
+    <t>Công ty TNHH VT</t>
+  </si>
+  <si>
+    <t>093yyzzxxx</t>
+  </si>
+  <si>
+    <t>vtgroup.com.jp</t>
+  </si>
+  <si>
+    <t>Vietnamese</t>
+  </si>
+  <si>
+    <t>Công ty CP YHL</t>
+  </si>
+  <si>
+    <t>Wakayama</t>
+  </si>
+  <si>
+    <t>640xyzy</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Công ty VT YHL</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
+  </si>
+  <si>
+    <t>Mua hàng qua app 12:19</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>30-06-2027</t>
+  </si>
+  <si>
+    <t>01-06-2027</t>
+  </si>
+  <si>
+    <t>30-06-2028</t>
+  </si>
+  <si>
+    <t>2384</t>
+  </si>
+  <si>
+    <t>Xây nhà cho bé</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>nhacuabe</t>
+  </si>
+  <si>
+    <t>Mái ấm của em, hạnh phúc của ta</t>
+  </si>
+  <si>
+    <t>Mua hàng qua app 12:11</t>
   </si>
 </sst>
 </file>
@@ -227,7 +323,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -239,6 +335,12 @@
         <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="none"/>
@@ -256,11 +358,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -652,7 +769,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1129EC2-D029-48F9-827C-BCE01AB8E176}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -672,7 +789,7 @@
         <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>33</v>
@@ -701,7 +818,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
@@ -716,10 +833,10 @@
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
@@ -739,7 +856,43 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -747,90 +900,241 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FC15DE-0E0A-485E-AD31-E7992A0D7BD7}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="3" width="16.5546875" style="5"/>
+    <col min="4" max="4" width="18.5546875" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="16.5546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" s="5" t="str">
         <f xml:space="preserve"> Customer!A2</f>
-        <v>Công ty Hải Lê</v>
-      </c>
-      <c r="D2" t="s">
+        <v>Công ty CP YHL</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="K2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3">
-        <f>Customer!N2</f>
-        <v>0</v>
+    <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f xml:space="preserve"> Customer!A2</f>
+        <v>Công ty CP YHL</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="6">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="8" t="str">
+        <f>B4</f>
+        <v>2384</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D796507-C72F-4C1A-9057-ECD9C2EB8BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696E2C84-142E-4740-A0C6-4B3FD7F38CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2136" yWindow="708" windowWidth="19944" windowHeight="11328" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="87">
   <si>
     <t>Project_Name</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Billing_Type</t>
   </si>
   <si>
-    <t>Mua hàng qua app</t>
-  </si>
-  <si>
     <t>Task Hours</t>
   </si>
   <si>
@@ -196,33 +193,12 @@
     <t>Japanese</t>
   </si>
   <si>
-    <t>Thạch cao</t>
-  </si>
-  <si>
     <t>Project_Number</t>
   </si>
   <si>
-    <t>Mua hàng online</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>01-05-2026</t>
-  </si>
-  <si>
-    <t>30-05-2026</t>
-  </si>
-  <si>
-    <t>online</t>
-  </si>
-  <si>
     <t>Ở đâu cũng mua được</t>
   </si>
   <si>
-    <t>2383</t>
-  </si>
-  <si>
     <t>Testcase</t>
   </si>
   <si>
@@ -268,9 +244,6 @@
     <t>Cancelled</t>
   </si>
   <si>
-    <t>Mua hàng qua app 12:19</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -286,22 +259,49 @@
     <t>30-06-2028</t>
   </si>
   <si>
-    <t>2384</t>
-  </si>
-  <si>
     <t>Xây nhà cho bé</t>
   </si>
   <si>
     <t>Not Started</t>
   </si>
   <si>
-    <t>nhacuabe</t>
-  </si>
-  <si>
     <t>Mái ấm của em, hạnh phúc của ta</t>
   </si>
   <si>
-    <t>Mua hàng qua app 12:11</t>
+    <t>ADD - EDIT</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nhacuabe </t>
+  </si>
+  <si>
+    <t>Mua hàng qua app 2026</t>
+  </si>
+  <si>
+    <t>2389</t>
+  </si>
+  <si>
+    <t>Mua hàng qua app 02/05/2026</t>
+  </si>
+  <si>
+    <t>2392</t>
+  </si>
+  <si>
+    <t>Tổ ấm nhỏ</t>
+  </si>
+  <si>
+    <t>https://crm.anhtester.com/admin/clients/client/9093</t>
+  </si>
+  <si>
+    <t>2393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thạch cao </t>
+  </si>
+  <si>
+    <t xml:space="preserve">online </t>
   </si>
 </sst>
 </file>
@@ -358,24 +358,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -789,7 +786,7 @@
         <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>33</v>
@@ -813,12 +810,12 @@
         <v>32</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
@@ -827,16 +824,16 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
@@ -845,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>20</v>
@@ -853,42 +850,46 @@
       <c r="L2" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="M2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
       </c>
       <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
         <v>49</v>
       </c>
-      <c r="G3" t="s">
-        <v>50</v>
-      </c>
       <c r="H3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -900,237 +901,201 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FC15DE-0E0A-485E-AD31-E7992A0D7BD7}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="16.5546875" style="5"/>
-    <col min="4" max="4" width="18.5546875" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="16.5546875" style="5"/>
+    <col min="1" max="3" width="16.5546875" style="3"/>
+    <col min="4" max="4" width="18.5546875" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="16.5546875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="5" t="s">
+      <c r="H1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="3" t="str">
+        <f xml:space="preserve"> Customer!A3</f>
+        <v>Công ty TNHH VT</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="str">
-        <f xml:space="preserve"> Customer!A2</f>
-        <v>Công ty CP YHL</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>46</v>
+      <c r="J2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <f xml:space="preserve"> Customer!A2</f>
-        <v>Công ty CP YHL</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="A3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="4">
+        <v>3</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>58</v>
+      <c r="J3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="A4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="5" t="str">
+        <f>B3</f>
+        <v>2389</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="G4" s="6">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="8" t="str">
-        <f>B4</f>
-        <v>2384</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="J6" s="6" t="s">
+      <c r="A5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>58</v>
+      <c r="D5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
   <si>
     <t>Project_Name</t>
   </si>
@@ -302,12 +302,16 @@
   </si>
   <si>
     <t xml:space="preserve">online </t>
+  </si>
+  <si>
+    <t>2396</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -323,7 +327,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -345,6 +349,9 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill/>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -358,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -375,6 +382,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -715,21 +725,21 @@
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -737,10 +747,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -748,10 +758,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -814,40 +824,40 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>44</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>34</v>
       </c>
       <c r="M2" s="7" t="s">
@@ -858,37 +868,37 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>57</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>62</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" t="s" s="0">
         <v>64</v>
       </c>
     </row>
@@ -904,9 +914,9 @@
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="16.5546875" style="3"/>
-    <col min="4" max="4" width="18.5546875" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="16.5546875" style="3"/>
+    <col min="1" max="3" style="3" width="16.5546875"/>
+    <col min="4" max="4" customWidth="true" style="3" width="18.5546875"/>
+    <col min="5" max="16384" style="3" width="16.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -1064,8 +1074,8 @@
       <c r="A5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>81</v>
+      <c r="B5" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>80</v>

--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -3,23 +3,24 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696E2C84-142E-4740-A0C6-4B3FD7F38CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70230AE2-7041-4CA6-B0ED-D659B755BDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2136" yWindow="708" windowWidth="19944" windowHeight="11328" activeTab="2" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
     <sheet name="Customer" sheetId="1" r:id="rId2"/>
     <sheet name="Project" sheetId="2" r:id="rId3"/>
+    <sheet name="Task" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="110">
   <si>
     <t>Project_Name</t>
   </si>
@@ -106,9 +107,6 @@
     <t>7000</t>
   </si>
   <si>
-    <t>TCs</t>
-  </si>
-  <si>
     <t>Email</t>
   </si>
   <si>
@@ -283,12 +281,6 @@
     <t>2389</t>
   </si>
   <si>
-    <t>Mua hàng qua app 02/05/2026</t>
-  </si>
-  <si>
-    <t>2392</t>
-  </si>
-  <si>
     <t>Tổ ấm nhỏ</t>
   </si>
   <si>
@@ -304,14 +296,88 @@
     <t xml:space="preserve">online </t>
   </si>
   <si>
-    <t>2396</t>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Hourly_Rate</t>
+  </si>
+  <si>
+    <t>Due_Date</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Repeat _Every</t>
+  </si>
+  <si>
+    <t>Related_To</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Assignees</t>
+  </si>
+  <si>
+    <t>Followers</t>
+  </si>
+  <si>
+    <t>Mua hàng qua app 05/2026</t>
+  </si>
+  <si>
+    <t>2398</t>
+  </si>
+  <si>
+    <t>Task Description</t>
+  </si>
+  <si>
+    <t>testAddNewTask_FromTaskPage</t>
+  </si>
+  <si>
+    <t>Meeting</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>testAddNewTask_FromProjectPage</t>
+  </si>
+  <si>
+    <t>Discuss</t>
+  </si>
+  <si>
+    <t>03/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nhanhotiennghi </t>
+  </si>
+  <si>
+    <t>Bàn về nguyên vật liệu</t>
+  </si>
+  <si>
+    <t>Lên plan</t>
+  </si>
+  <si>
+    <t>AssigneesProject ManagerAdmin Anh TesterAdmin Example</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -350,7 +416,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="1">
@@ -365,26 +431,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -723,49 +801,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D93C7CD2-8E73-43DE-94E6-3A28F5CAF450}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="21.77734375" style="4"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s" s="0">
+      <c r="A1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s" s="0">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="B2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s" s="0">
+      <c r="C3" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -784,7 +865,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
@@ -796,10 +877,10 @@
         <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>11</v>
@@ -817,89 +898,89 @@
         <v>15</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>61</v>
+      <c r="A2" t="s">
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
         <v>43</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>44</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>83</v>
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" t="s" s="0">
-        <v>57</v>
+      <c r="A3" t="s">
+        <v>56</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
         <v>58</v>
       </c>
-      <c r="D3" t="s" s="0">
-        <v>59</v>
-      </c>
-      <c r="E3" t="s" s="0">
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s" s="0">
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
         <v>48</v>
       </c>
-      <c r="G3" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="H3" t="s" s="0">
+      <c r="H3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I3" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" t="s">
         <v>63</v>
-      </c>
-      <c r="L3" t="s" s="0">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -914,198 +995,198 @@
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" style="3" width="16.5546875"/>
-    <col min="4" max="4" customWidth="true" style="3" width="18.5546875"/>
-    <col min="5" max="16384" style="3" width="16.5546875"/>
+    <col min="1" max="3" width="16.5546875" style="6"/>
+    <col min="4" max="4" width="18.5546875" style="6" customWidth="1"/>
+    <col min="5" max="16384" width="16.5546875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="3" t="str">
+      <c r="B2" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="6" t="str">
         <f xml:space="preserve"> Customer!A3</f>
         <v>Công ty TNHH VT</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>45</v>
+      <c r="J2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="G3" s="7">
         <v>3</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>51</v>
+      <c r="H3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="5" t="str">
+      <c r="A4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="8" t="str">
         <f>B3</f>
         <v>2389</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J4" s="4" t="s">
+      <c r="H5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>51</v>
+      <c r="K5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1113,4 +1194,154 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20CCAF4C-440A-4CC0-BE66-266F410C1500}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="20.77734375" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="10" t="str">
+        <f xml:space="preserve"> Project!B2</f>
+        <v>2393</v>
+      </c>
+      <c r="J2" s="10" t="str">
+        <f xml:space="preserve"> Project!C2</f>
+        <v>Tổ ấm nhỏ</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="10" t="str">
+        <f xml:space="preserve"> Project!B4</f>
+        <v>2389</v>
+      </c>
+      <c r="J3" s="10" t="str">
+        <f xml:space="preserve"> Project!C4</f>
+        <v>Xây nhà cho bé</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
+++ b/src/test/resources/dataTest/dataProjectCuoiKhoa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anhTester\Project_Cuoi_Khoa\src\test\resources\dataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70230AE2-7041-4CA6-B0ED-D659B755BDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DDE3D3-9DFB-46A7-A48E-DB707E572B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D4AABB89-EE12-468A-B216-C59207BCAFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="111">
   <si>
     <t>Project_Name</t>
   </si>
@@ -372,6 +372,9 @@
   </si>
   <si>
     <t>AssigneesProject ManagerAdmin Anh TesterAdmin Example</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
 </sst>
 </file>
@@ -857,7 +860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1129EC2-D029-48F9-827C-BCE01AB8E176}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -980,6 +983,38 @@
         <v>62</v>
       </c>
       <c r="L3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" t="s">
         <v>63</v>
       </c>
     </row>
